--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260728.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260728.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>28.43%</t>
+          <t>28.71%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.40%</t>
+          <t>8.08%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.43%</t>
+          <t>6.54%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.81%</t>
+          <t>5.94%</t>
         </is>
       </c>
     </row>
@@ -704,51 +704,51 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.17%</t>
+          <t>4.85%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>SO US</t>
+          <t>NOW US</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>南方公司</t>
+          <t>ServiceNow Inc</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>73,105</t>
+          <t>66,320</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.41%</t>
+          <t>3.61%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>NOW US</t>
+          <t>SO US</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>ServiceNow Inc</t>
+          <t>南方公司</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>66,320</t>
+          <t>73,105</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.39%</t>
+          <t>3.48%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>3.22%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.21%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>2.81%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.65%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.30%</t>
         </is>
       </c>
     </row>
@@ -880,95 +880,95 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.15%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>HPE US</t>
+          <t>D US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>慧與</t>
+          <t>道明尼能源公司</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>85,615</t>
+          <t>56,845</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>D US</t>
+          <t>HPE US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>道明尼能源公司</t>
+          <t>慧與</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>56,845</t>
+          <t>85,615</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>1.92%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>21,690</t>
+          <t>29,548</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>29,548</t>
+          <t>21,690</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.59%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.59%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
@@ -1034,90 +1034,90 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>8,790</t>
+          <t>141,205</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>141,205</t>
+          <t>2,514,827</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>12,951</t>
+          <t>20,515</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>20,515</t>
+          <t>8,790</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,88 +1129,88 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>10,666</t>
+          <t>12,951</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>17,671</t>
+          <t>10,666</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>41,880</t>
+          <t>17,671</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>13,105</t>
+          <t>41,880</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -1232,29 +1232,29 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>21,787</t>
+          <t>13,105</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1276,29 +1276,29 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>1,224,092</t>
+          <t>21,787</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
@@ -1319,28 +1319,6 @@
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>RDI_USD</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>1,290,734</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
